--- a/Participants/3_Workflow_B_Operations_and_Analytics/GBF_Performance_Dashboard.xlsx
+++ b/Participants/3_Workflow_B_Operations_and_Analytics/GBF_Performance_Dashboard.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis DB3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis DB4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="On-request A" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="On-request B" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clean Data" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,10 @@
     <font>
       <b val="1"/>
       <color rgb="001B2A4A"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
     </font>
   </fonts>
   <fills count="2">
@@ -60,10 +64,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -476,7 +481,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Task DB-2: Build pivot tables on the Dashboard tab.</t>
+          <t>Foundation (B2): Build pivot tables on the Dashboard tab.</t>
         </is>
       </c>
     </row>
@@ -507,45 +512,66 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Task DB-3: Attendance vs outcomes on Analysis DB3 tab.</t>
+          <t>On-request deep dives (only if A's Demand / R-xx needs them):</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Task DB-4: Mentor hours vs completion on Analysis DB4 tab.</t>
+          <t xml:space="preserve">  - Use scratch tabs 'On-request A' and 'On-request B' for working analysis</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Design the method yourself from the data dictionary; Buddy coaches, does not prescribe</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rules:</t>
+          <t xml:space="preserve">  - Return results via Findings Memos - not by sharing this workbook with A</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - State your placement definition on the Dashboard tab</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Log cleaning decisions in the Shared Toolkit Assumption Log</t>
+          <t>Rules:</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  - State your placement definition on the Dashboard tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Log cleaning decisions in the Shared Toolkit Assumption Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t xml:space="preserve">  - Never delete outliers without documenting why</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Follow Estate → Demand → Plan → R/FM before pushing decision numbers to A</t>
         </is>
       </c>
     </row>
@@ -580,7 +606,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sample note: export covers ~520 records; org total 2,847 per D-01.</t>
+          <t>Definition note: primary 65% rate uses completion_status = Completed (completers). Blank placed_90d = missing follow-up, not 'not placed'. Report Formal and Broad.</t>
         </is>
       </c>
     </row>
@@ -602,20 +628,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Attendance and placement (DB-3)</t>
+          <t>On-request analysis workspace A</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Use only if a Demand / R-xx requires it (e.g. attendance vs placement). Normalise codes; name confounders in the Findings Memo. You own the method.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Your analysis goes here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Linked Demand / R-xx / AP-xx: ________________________________</t>
         </is>
       </c>
     </row>
@@ -630,20 +670,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mentor hours and completion (DB-4)</t>
+          <t>On-request analysis workspace B</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Use only if a Demand / R-xx requires it (e.g. mentor hours vs completion). Filter volunteer_hours.status = Active (or justify including Inactive / M-099). You own the method - do not claim causation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Your analysis goes here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Linked Demand / R-xx / AP-xx: ________________________________</t>
         </is>
       </c>
     </row>
@@ -658,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,9 +723,23 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Keep a copy of raw elsewhere. Log every cleaning rule in the Assumption Log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Your analysis goes here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Linked Demand / R-xx / AP-xx: ________________________________</t>
         </is>
       </c>
     </row>
